--- a/template/12.4/量化业务日报-2025-12-04.xlsx
+++ b/template/12.4/量化业务日报-2025-12-04.xlsx
@@ -38,7 +38,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,26 +63,8 @@
         <bgColor rgb="00DAEEF3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FADADE"/>
-        <bgColor rgb="00FADADE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2D9"/>
-        <bgColor rgb="00E3F2D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4D1"/>
-        <bgColor rgb="00FFF4D1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -137,22 +119,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,20 +168,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -988,7 +949,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1.00394</v>
+        <v>1.00495</v>
       </c>
     </row>
     <row r="19">
@@ -1009,7 +970,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>0.10084%</t>
+          <t>0.00024%</t>
         </is>
       </c>
     </row>
@@ -1020,7 +981,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.99676</v>
+        <v>0.99777</v>
       </c>
     </row>
     <row r="22">
@@ -1041,7 +1002,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>0.10167%</t>
+          <t>0.00035%</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1328,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>1.00512</v>
+        <v>1.00526</v>
       </c>
     </row>
     <row r="19" ht="27" customHeight="1">
@@ -1388,7 +1349,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>0.01375%</t>
+          <t>-0.00018%</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1360,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.99794</v>
+        <v>0.99808</v>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
@@ -1420,7 +1381,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>0.01396%</t>
+          <t>-7e-05%</t>
         </is>
       </c>
     </row>
@@ -1587,8 +1548,12 @@
           <t>一、账户资产及收益情况</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="27" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -1601,7 +1566,11 @@
           <t>量化三</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1612,7 +1581,11 @@
       <c r="B4" s="6" t="n">
         <v>85016</v>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>账户编号</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1622,12 +1595,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>量化三投机</t>
+          <t>量化三股票单元</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>量化三股票单元</t>
+          <t>资产单元名称</t>
         </is>
       </c>
     </row>
@@ -1638,10 +1611,12 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4129461.01</v>
-      </c>
-      <c r="C6" s="7" t="n">
         <v>852777.36</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>单元资产净值</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
@@ -1651,9 +1626,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4982238.37</v>
-      </c>
-      <c r="C7" s="4" t="n"/>
+        <v>852777.36</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>账户资产净值</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1662,10 +1641,12 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26883.09</v>
-      </c>
-      <c r="C8" s="7" t="n">
         <v>3765.01</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>返息、逆回购</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -1674,62 +1655,84 @@
           <t>手续费</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>5177.13</v>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>手续费</t>
         </is>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>-17761.63</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>收益率(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>-0.3552%</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>-53586.86</v>
-      </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>收益率(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>-1.0717%</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1737,8 +1740,12 @@
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1747,9 +1754,13 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C15" s="4" t="n"/>
+        <v>10000000</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1758,9 +1769,13 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>4982238.37</v>
-      </c>
-      <c r="C16" s="4" t="n"/>
+        <v>852777.36</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>资产净值</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1769,9 +1784,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C17" s="4" t="n"/>
+        <v>10000000</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1782,7 +1801,11 @@
       <c r="B18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1791,9 +1814,13 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>0.99694</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
+        <v>-1</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -1802,9 +1829,13 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>0.9964499999999999</v>
-      </c>
-      <c r="C20" s="4" t="n"/>
+        <v>0.08527999999999999</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -1814,10 +1845,14 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>-0.04938%</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
+          <t>-108.52777%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
@@ -1826,33 +1861,47 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.98978</v>
-      </c>
-      <c r="C22" s="4" t="n"/>
+        <v>-1</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>单位净值(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
-        <v>0.98928</v>
-      </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>日净值增长率(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>-0.05025%</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="27" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1860,8 +1909,12 @@
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="27" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1869,8 +1922,10 @@
           <t>占用</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>0</v>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1884,8 +1939,10 @@
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>4129461.01</v>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1899,9 +1956,9 @@
           <t>风险度</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>风险度</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1916,8 +1973,12 @@
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="175" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -1948,8 +2009,12 @@
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="125" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1974,28 +2039,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="B4"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="B3"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="B23"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="B13"/>
+    <mergeCell ref="B10"/>
+    <mergeCell ref="B19"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2039,8 +2104,12 @@
           <t>一、账户资产及收益情况</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>一、账户资产及收益情况</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="27" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -2053,7 +2122,11 @@
           <t>量化三</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -2064,7 +2137,11 @@
       <c r="B4" s="6" t="n">
         <v>85016</v>
       </c>
-      <c r="C4" s="4" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>账户编号</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -2074,12 +2151,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>量化三投机</t>
+          <t>量化三股票单元</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>量化三股票单元</t>
+          <t>资产单元名称</t>
         </is>
       </c>
     </row>
@@ -2090,10 +2167,12 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>4129460.6</v>
-      </c>
-      <c r="C6" s="7" t="n">
         <v>852777.36</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>单元资产净值</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1">
@@ -2103,9 +2182,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4982237.96</v>
-      </c>
-      <c r="C7" s="4" t="n"/>
+        <v>852777.36</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>账户资产净值</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="27" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -2114,10 +2197,12 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26883.09</v>
-      </c>
-      <c r="C8" s="7" t="n">
         <v>3765.01</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>返息、逆回购</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1">
@@ -2126,12 +2211,14 @@
           <t>手续费</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>5177.13</v>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>手续费</t>
+        </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>手续费</t>
         </is>
       </c>
     </row>
@@ -2142,35 +2229,47 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>-20539.4</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>2777.36</v>
+        <v>-147222.64</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>-17762.04000000004</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>收益率(含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>-0.3552%</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>收益率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -2179,35 +2278,47 @@
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>-52599.6199999999</v>
-      </c>
-      <c r="C13" s="11" t="n">
         <v>-987.66</v>
       </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
-        <v>-53587.27000000003</v>
-      </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>总盈利/亏损(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>收益率(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>-1.0717%</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>收益率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="27" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -2215,8 +2326,12 @@
           <t>二、净值列示</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>二、净值列示</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -2225,9 +2340,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C17" s="4" t="n"/>
+        <v>10000000</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2236,9 +2355,13 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>4982237.96</v>
-      </c>
-      <c r="C18" s="4" t="n"/>
+        <v>852777.36</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>资产净值</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="27" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2247,9 +2370,13 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
+        <v>10000000</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>总份额</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="27" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2260,7 +2387,11 @@
       <c r="B20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="4" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>期初单位净值</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -2271,7 +2402,11 @@
       <c r="B21" s="12" t="n">
         <v>0.99694</v>
       </c>
-      <c r="C21" s="4" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="27" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -2280,9 +2415,13 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>0.9964499999999999</v>
-      </c>
-      <c r="C22" s="4" t="n"/>
+        <v>0.08527999999999999</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="27" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -2292,10 +2431,14 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>-0.04939%</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
+          <t>-91.44605%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
@@ -2306,31 +2449,45 @@
       <c r="B24" s="13" t="n">
         <v>0.98978</v>
       </c>
-      <c r="C24" s="4" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>昨日单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="27" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>单位净值(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
-        <v>0.98928</v>
-      </c>
-      <c r="C25" s="4" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>单位净值(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="27" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>日净值增长率(不含返息、逆回购、手续费)</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>-0.05026%</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>日净值增长率(不含返息、逆回购、手续费)</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="27" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -2338,8 +2495,12 @@
           <t>三、保证金使用情况</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>三、保证金使用情况</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2347,8 +2508,10 @@
           <t>占用</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>0</v>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>占用</t>
+        </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2362,8 +2525,10 @@
           <t>账户权益</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n">
-        <v>4129460.6</v>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>账户权益</t>
+        </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2377,9 +2542,9 @@
           <t>风险度</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>风险度</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2394,8 +2559,12 @@
           <t>四、交易情况</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>四、交易情况</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="175" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -2426,8 +2595,12 @@
           <t>五、持仓情况</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>五、持仓情况</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="125" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2450,30 +2623,32 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="27" customHeight="1"/>
+    <row r="36" ht="27" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B15"/>
+    <mergeCell ref="B24"/>
+    <mergeCell ref="B20"/>
+    <mergeCell ref="B4"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B26"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="B25"/>
+    <mergeCell ref="B3"/>
+    <mergeCell ref="B22"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="B12"/>
+    <mergeCell ref="B18"/>
+    <mergeCell ref="B21"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="B11"/>
+    <mergeCell ref="B14"/>
+    <mergeCell ref="B23"/>
+    <mergeCell ref="B17"/>
+    <mergeCell ref="B19"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2496,28 +2671,28 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="18" t="n"/>
-      <c r="D1" s="18" t="n"/>
+      <c r="B1" s="17" t="n"/>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="17" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
@@ -2551,15 +2726,9 @@
           <t>农副</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>80.45999999999999</v>
-      </c>
-      <c r="C4" s="20" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="D4" s="21" t="n">
-        <v>32.81</v>
-      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2567,15 +2736,9 @@
           <t>有色</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>42.85</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>126.34</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>-83.48999999999999</v>
-      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2583,15 +2746,9 @@
           <t>能化</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>76.78</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>371.18</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>-294.4</v>
-      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2599,15 +2756,9 @@
           <t>黑色</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>305.38</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>58.03</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>247.35</v>
-      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2615,15 +2766,9 @@
           <t>贵金属</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2631,15 +2776,9 @@
           <t>股指期货</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>88.95999999999999</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>-88.95999999999999</v>
-      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2647,15 +2786,9 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>5.51</v>
-      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2663,99 +2796,93 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
-        <v>510.99</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>692.17</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>-181.18</v>
-      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>10.1731%</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="17" t="n">
         <v>1004.95</v>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="17" t="n">
         <v>0.14</v>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="17" t="n">
         <v>1203.16</v>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
-        <v>1203.16</v>
-      </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
+      <c r="B17" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="17" t="n">
         <v>-0.09</v>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2771,7 +2898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2782,25 +2909,25 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
@@ -2834,20 +2961,9 @@
           <t>农副</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>80.45999999999999</v>
-      </c>
-      <c r="C4" s="20" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="D4" s="21" t="n">
-        <v>32.81</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>菜籽油2601, 菜粕2605, 白糖2601, 豆一号2601, 鲜鸡蛋2601, 棉花2601, 苹果2605, 豆粕2605, 玉米淀粉2601, 玉米2601, 豆油2605</t>
-        </is>
-      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2855,20 +2971,9 @@
           <t>有色</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>42.85</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>126.34</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>-83.48999999999999</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>镍2601, 不锈钢2601, 铝2601, 氧化铝2601, 锡2601, 工业硅2601, 铅2601, 锌2601</t>
-        </is>
-      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2876,20 +2981,9 @@
           <t>能化</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>76.78</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>371.18</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>-294.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>聚乙烯2601, 玻璃2601, 甲醇N2601, 纯碱2601, 聚氯乙烯2601, PTA2601, 天然橡胶2605, 乙二醇2601, 聚丙烯2601, 苯乙烯2601, 尿素2601, 石油沥青2602</t>
-        </is>
-      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2897,20 +2991,9 @@
           <t>黑色</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>305.38</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>58.03</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>247.35</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>焦煤2601, 焦炭2601, 铁矿石2601, 热轧卷板2605, 螺纹钢2605, 锰硅2601, 硅铁2603</t>
-        </is>
-      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2918,16 +3001,9 @@
           <t>贵金属</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2935,20 +3011,9 @@
           <t>股指期货</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>88.95999999999999</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>-88.95999999999999</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>IH2512</t>
-        </is>
-      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2956,20 +3021,9 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>漂白硫酸盐针叶木浆2605</t>
-        </is>
-      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2977,100 +3031,93 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
-        <v>510.99</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>692.17</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>-181.18</v>
-      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>10.1731%</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="17" t="n">
         <v>1004.95</v>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="17" t="n">
         <v>0.14</v>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="17" t="n">
         <v>1203.16</v>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
-        <v>1203.16</v>
-      </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="B17" s="17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="17" t="n">
         <v>-0.09</v>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
